--- a/Employee_Reports_wi48/Alby Manchandiyil Antony Q0599.xlsx
+++ b/Employee_Reports_wi48/Alby Manchandiyil Antony Q0599.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
